--- a/artfynd/A 42301-2022 artfynd.xlsx
+++ b/artfynd/A 42301-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115305779</v>
+        <v>115306508</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Lillterrsjö (Södra Lillterrsjö), Ång</t>
+          <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579550</v>
+        <v>579547</v>
       </c>
       <c r="R2" t="n">
-        <v>7058969</v>
+        <v>7058905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115306078</v>
+        <v>115305779</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,32 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Lillterrsjö (Södra Lillterrsjö), Ång</t>
+          <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115306840</v>
+        <v>115306078</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,19 +920,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Lillterrsjö (Södra Lillterrsjö), Ång</t>
+          <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579544</v>
+        <v>579550</v>
       </c>
       <c r="R4" t="n">
-        <v>7058939</v>
+        <v>7058969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115306508</v>
+        <v>115306840</v>
       </c>
       <c r="B5" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Lillterrsjö (Södra Lillterrsjö), Ång</t>
+          <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579547</v>
+        <v>579544</v>
       </c>
       <c r="R5" t="n">
-        <v>7058905</v>
+        <v>7058939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1110,118 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115305589</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Lillterrsjö, Södra Lillterrsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579555</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7058997</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42301-2022 artfynd.xlsx
+++ b/artfynd/A 42301-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115306508</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115305779</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115306078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115306840</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115305589</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>